--- a/ReportWebSite/Reports1NF/Templates/prognoz_zvit.xlsx
+++ b/ReportWebSite/Reports1NF/Templates/prognoz_zvit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DKVSOURCESFINALEDITION_v20\ReportWebSite\Reports1NF\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D38155B6-EF1A-4164-A910-2D56F1B3F3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7808CDFB-9513-4217-9273-3A6522A227D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>№ з/п</t>
   </si>
@@ -109,28 +109,43 @@
     <t>Загальна кількість балансоутримувачів</t>
   </si>
   <si>
-    <t xml:space="preserve">у тому числі кількість балансоутримувачів, які здійснюють нарахування орендної плати </t>
-  </si>
-  <si>
-    <t>у тому числі кількість зобовязаних сплачувати до бюджету</t>
-  </si>
-  <si>
-    <t>Нараховано орендної плати за 2024, тис. грн. (без ПДВ)
-(*) - екстраполяція</t>
-  </si>
-  <si>
-    <t>Нараховано орендної плати балансоутримувачами, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн за 2024 год (без ПДВ)
-(*) - екстраполяція</t>
-  </si>
-  <si>
     <t>Прогнозні показники надходжень від оренди та перерахування її частини до бюджету у 2025 р.</t>
   </si>
   <si>
-    <t>Надходження орендної плати на рахунки балансоутримувачів, зобов'язаних сплачувати 50% до бюджету м. Києва за 2024 год, тис. грн (без ПДВ)
-(*) - екстраполяція</t>
-  </si>
-  <si>
-    <t>Очікуваний (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2025 год, тис. Грн</t>
+    <t>кількість балансоутримувачів, які здійснюють нарахування орендної плати</t>
+  </si>
+  <si>
+    <t>кількість зобов"язаних сплачувати 50% надходжень орендної плати до бюджету м. Києва</t>
+  </si>
+  <si>
+    <t>НАРАХОВАНО орендної плати у останньому звітному периоди всіма балансоутримувавами, майно яких передано в оренду, тис. грн. (без ПДВ)</t>
+  </si>
+  <si>
+    <t>ОТРИМАНО орендної плати у останньому звітному периоди всіма балансоутримувавами, майно яких передано в оренду, тис. грн. (без ПДВ)</t>
+  </si>
+  <si>
+    <t>Нараховано орендної плати балансоутримувачами, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн за останньому звітному периоди (без ПДВ)</t>
+  </si>
+  <si>
+    <t>ОТРИМАНО орендної плати балансоутримувачами, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн за останньому звітному периоди (без ПДВ)</t>
+  </si>
+  <si>
+    <t>ПРОГНОЗ Нараховань орендної плати на рахунки всіх балансоутримувачів - отримувачів орендної плати за 2025 год, тис. грн (без ПДВ)</t>
+  </si>
+  <si>
+    <t>ПРОГНОЗ Нарахувань орендної плати на рахунки балансоутримувачів - отримувачів орендної плати за 2025 год, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн (без ПДВ)</t>
+  </si>
+  <si>
+    <t>Очікуваний (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2025 рік, тис. Грн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2026 рік, тис. грн  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2027 рік, тис. грн </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2028 рік, тис. грн  </t>
   </si>
 </sst>
 </file>
@@ -724,16 +739,16 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1025,7 +1040,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
@@ -1036,62 +1051,97 @@
     <col min="7" max="7" width="23.42578125" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="23.42578125" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="23.42578125" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="13" max="13" width="23.42578125" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+    </row>
+    <row r="2" spans="1:15" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="G2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="22" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+    </row>
+    <row r="4" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1119,8 +1169,26 @@
       <c r="I4" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>11</v>
+      </c>
+      <c r="L4" s="5">
+        <v>12</v>
+      </c>
+      <c r="M4" s="5">
+        <v>13</v>
+      </c>
+      <c r="N4" s="5">
+        <v>14</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1134,8 +1202,14 @@
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+    </row>
+    <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1149,8 +1223,14 @@
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
-    </row>
-    <row r="7" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="14"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+    </row>
+    <row r="7" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -1162,8 +1242,14 @@
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J7" s="16"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+    </row>
+    <row r="8" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -1177,8 +1263,14 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-    </row>
-    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="14"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -1192,8 +1284,14 @@
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-    </row>
-    <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="14"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -1207,8 +1305,14 @@
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-    </row>
-    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="14"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6</v>
       </c>
@@ -1222,8 +1326,14 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
-    </row>
-    <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="14"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>7</v>
       </c>
@@ -1237,8 +1347,14 @@
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
-    </row>
-    <row r="13" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="14"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+    </row>
+    <row r="13" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -1252,8 +1368,14 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+    </row>
+    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -1267,8 +1389,14 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="1:9" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="14"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+    </row>
+    <row r="15" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
@@ -1278,8 +1406,14 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-    </row>
-    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+    </row>
+    <row r="16" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>10</v>
       </c>
@@ -1293,8 +1427,14 @@
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
-    </row>
-    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="14"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>11</v>
       </c>
@@ -1308,8 +1448,14 @@
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
-    </row>
-    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="14"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -1323,8 +1469,14 @@
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="14"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>1</v>
       </c>
@@ -1336,8 +1488,14 @@
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
-    </row>
-    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+    </row>
+    <row r="20" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>13</v>
       </c>
@@ -1351,8 +1509,14 @@
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J20" s="14"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -1366,8 +1530,14 @@
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
-    </row>
-    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="14"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+    </row>
+    <row r="22" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>15</v>
       </c>
@@ -1381,8 +1551,14 @@
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
-    </row>
-    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J22" s="14"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+    </row>
+    <row r="23" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>16</v>
       </c>
@@ -1396,8 +1572,14 @@
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J23" s="14"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+    </row>
+    <row r="24" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>17</v>
       </c>
@@ -1411,8 +1593,14 @@
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
-    </row>
-    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J24" s="14"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+    </row>
+    <row r="25" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>18</v>
       </c>
@@ -1426,8 +1614,14 @@
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="14"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+    </row>
+    <row r="26" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>19</v>
       </c>
@@ -1441,8 +1635,14 @@
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="14"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+    </row>
+    <row r="27" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>20</v>
       </c>
@@ -1456,8 +1656,14 @@
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="14"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+    </row>
+    <row r="28" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>21</v>
       </c>
@@ -1471,8 +1677,14 @@
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="14"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+    </row>
+    <row r="29" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>22</v>
       </c>
@@ -1486,8 +1698,14 @@
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J29" s="14"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+    </row>
+    <row r="30" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
         <v>2</v>
       </c>
@@ -1499,8 +1717,14 @@
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
-    </row>
-    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="19"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+    </row>
+    <row r="31" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>3</v>
       </c>
@@ -1512,14 +1736,21 @@
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="G2:G3"/>
+  <mergeCells count="19">
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -1528,6 +1759,11 @@
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>

--- a/ReportWebSite/Reports1NF/Templates/prognoz_zvit.xlsx
+++ b/ReportWebSite/Reports1NF/Templates/prognoz_zvit.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DKVSOURCESFINALEDITION_v20\ReportWebSite\Reports1NF\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7808CDFB-9513-4217-9273-3A6522A227D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EFBA7F-1D7C-4C5C-90ED-B4EA77A8DCCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>№ з/п</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2028 рік, тис. грн  </t>
+  </si>
+  <si>
+    <t>Нараховано орендної плати балансоутримувачами, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн за останньому звітному періоди (без ПДВ) без урахування діючих пільг</t>
   </si>
 </sst>
 </file>
@@ -745,17 +748,17 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1040,7 +1043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
@@ -1051,34 +1054,36 @@
     <col min="7" max="7" width="23.42578125" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="23.42578125" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="23.42578125" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="23.42578125" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
       <c r="G1" s="21"/>
       <c r="H1" s="21"/>
       <c r="I1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="J1" s="21"/>
       <c r="L1" s="21"/>
       <c r="M1" s="21"/>
       <c r="N1" s="21"/>
       <c r="O1" s="21"/>
-    </row>
-    <row r="2" spans="1:15" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="P1" s="21"/>
+    </row>
+    <row r="2" spans="1:16" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
@@ -1106,26 +1111,29 @@
         <v>35</v>
       </c>
       <c r="J2" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="M2" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="N2" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="O2" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+    <row r="3" spans="1:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
@@ -1140,8 +1148,9 @@
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
       <c r="O3" s="23"/>
-    </row>
-    <row r="4" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="23"/>
+    </row>
+    <row r="4" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1187,8 +1196,11 @@
       <c r="O4" s="5">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P4" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1202,14 +1214,15 @@
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="14"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
-    </row>
-    <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="15"/>
+    </row>
+    <row r="6" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1223,14 +1236,15 @@
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="14"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
-    </row>
-    <row r="7" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="15"/>
+    </row>
+    <row r="7" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -1242,14 +1256,15 @@
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="16"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
-    </row>
-    <row r="8" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="17"/>
+    </row>
+    <row r="8" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -1263,14 +1278,15 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="14"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
-    </row>
-    <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="15"/>
+    </row>
+    <row r="9" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -1284,14 +1300,15 @@
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="14"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
-    </row>
-    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="15"/>
+    </row>
+    <row r="10" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -1305,14 +1322,15 @@
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="14"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
-    </row>
-    <row r="11" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="15"/>
+    </row>
+    <row r="11" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6</v>
       </c>
@@ -1326,14 +1344,15 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="14"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
-    </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="15"/>
+    </row>
+    <row r="12" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>7</v>
       </c>
@@ -1347,14 +1366,15 @@
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="14"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
-    </row>
-    <row r="13" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="15"/>
+    </row>
+    <row r="13" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -1368,14 +1388,15 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="14"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
-    </row>
-    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="15"/>
+    </row>
+    <row r="14" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -1389,14 +1410,15 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="14"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
-    </row>
-    <row r="15" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="15"/>
+    </row>
+    <row r="15" spans="1:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
@@ -1412,8 +1434,9 @@
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
-    </row>
-    <row r="16" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="18"/>
+    </row>
+    <row r="16" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>10</v>
       </c>
@@ -1427,14 +1450,15 @@
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="14"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-    </row>
-    <row r="17" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="15"/>
+    </row>
+    <row r="17" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>11</v>
       </c>
@@ -1448,14 +1472,15 @@
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="14"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
-    </row>
-    <row r="18" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="15"/>
+    </row>
+    <row r="18" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -1469,18 +1494,19 @@
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="14"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
-    </row>
-    <row r="19" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="P18" s="15"/>
+    </row>
+    <row r="19" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="27"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -1488,14 +1514,15 @@
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="19"/>
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
-    </row>
-    <row r="20" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="20"/>
+    </row>
+    <row r="20" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>13</v>
       </c>
@@ -1509,14 +1536,15 @@
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="14"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
-    </row>
-    <row r="21" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="15"/>
+    </row>
+    <row r="21" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -1530,14 +1558,15 @@
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="14"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
-    </row>
-    <row r="22" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="15"/>
+    </row>
+    <row r="22" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>15</v>
       </c>
@@ -1551,14 +1580,15 @@
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="14"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
-    </row>
-    <row r="23" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="15"/>
+    </row>
+    <row r="23" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>16</v>
       </c>
@@ -1572,14 +1602,15 @@
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="14"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
-    </row>
-    <row r="24" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="15"/>
+    </row>
+    <row r="24" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>17</v>
       </c>
@@ -1593,14 +1624,15 @@
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="14"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
-    </row>
-    <row r="25" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="15"/>
+    </row>
+    <row r="25" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>18</v>
       </c>
@@ -1614,14 +1646,15 @@
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="14"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
-    </row>
-    <row r="26" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="15"/>
+    </row>
+    <row r="26" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>19</v>
       </c>
@@ -1635,14 +1668,15 @@
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="14"/>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
-    </row>
-    <row r="27" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="15"/>
+    </row>
+    <row r="27" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>20</v>
       </c>
@@ -1656,14 +1690,15 @@
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="14"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
-    </row>
-    <row r="28" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="15"/>
+    </row>
+    <row r="28" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>21</v>
       </c>
@@ -1677,14 +1712,15 @@
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="14"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
-    </row>
-    <row r="29" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="15"/>
+    </row>
+    <row r="29" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>22</v>
       </c>
@@ -1698,18 +1734,19 @@
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="14"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
-    </row>
-    <row r="30" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="P29" s="15"/>
+    </row>
+    <row r="30" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="25"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -1717,18 +1754,19 @@
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="19"/>
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
       <c r="O30" s="20"/>
-    </row>
-    <row r="31" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
+      <c r="P30" s="20"/>
+    </row>
+    <row r="31" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="26"/>
+      <c r="B31" s="24"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -1736,21 +1774,22 @@
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="19"/>
       <c r="L31" s="20"/>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
       <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="O2:O3"/>
+  <mergeCells count="20">
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="G2:G3"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -1759,11 +1798,12 @@
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>

--- a/ReportWebSite/Reports1NF/Templates/prognoz_zvit.xlsx
+++ b/ReportWebSite/Reports1NF/Templates/prognoz_zvit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DKVSOURCESFINALEDITION_v20\ReportWebSite\Reports1NF\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EFBA7F-1D7C-4C5C-90ED-B4EA77A8DCCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AD990A-77B0-427F-B860-3CC11CE81006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>№ з/п</t>
   </si>
@@ -130,25 +130,31 @@
     <t>ОТРИМАНО орендної плати балансоутримувачами, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн за останньому звітному периоди (без ПДВ)</t>
   </si>
   <si>
-    <t>ПРОГНОЗ Нараховань орендної плати на рахунки всіх балансоутримувачів - отримувачів орендної плати за 2025 год, тис. грн (без ПДВ)</t>
-  </si>
-  <si>
-    <t>ПРОГНОЗ Нарахувань орендної плати на рахунки балансоутримувачів - отримувачів орендної плати за 2025 год, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн (без ПДВ)</t>
-  </si>
-  <si>
-    <t>Очікуваний (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2025 рік, тис. Грн</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2026 рік, тис. грн  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2027 рік, тис. грн </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2028 рік, тис. грн  </t>
-  </si>
-  <si>
-    <t>Нараховано орендної плати балансоутримувачами, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн за останньому звітному періоди (без ПДВ) без урахування діючих пільг</t>
+    <t>Нараховано 100% орендної плати всіма балансоутримувачами</t>
+  </si>
+  <si>
+    <t>Нараховано 100% орендної плати балансоутримувачами зобовязаними сплачувати 50% до бюджету</t>
+  </si>
+  <si>
+    <t>Нараховано  100% орендної плати балансоутримувачами звільненими від сплати 50% О.П. до бюджету</t>
+  </si>
+  <si>
+    <t>ПРОГНОЗ Нарахувань орендної плати на рахунки балансоутримувачів - отримувачів орендної плати за 2026 год, які зобов'язані сплачувати 50% до бюджету м. Києва, тис. грн (без ПДВ)</t>
+  </si>
+  <si>
+    <t>Очікуваний (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2026 рік, тис. Грн</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2027 рік, тис. грн  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2028 рік, тис. грн </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОГНОЗНИЙ (розрахунковий) показник надходжень 50%  від орендної плати до бюджету міста Києва на 2029 рік, тис. грн  </t>
+  </si>
+  <si>
+    <t>ПРОГНОЗ Нараховань орендної плати на рахунки всіх балансоутримувачів - отримувачів орендної плати за 2026 год, тис. грн (без ПДВ) без урахування діючих пільг</t>
   </si>
 </sst>
 </file>
@@ -748,17 +754,17 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1043,47 +1049,48 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="4" width="16.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" customWidth="1"/>
-    <col min="10" max="10" width="25.28515625" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" customWidth="1"/>
-    <col min="13" max="13" width="26" customWidth="1"/>
-    <col min="14" max="14" width="23.42578125" customWidth="1"/>
-    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="6" max="9" width="21.85546875" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="13" width="23.42578125" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="24.5703125" customWidth="1"/>
     <col min="16" max="16" width="23.42578125" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
+    <col min="18" max="18" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
       <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
       <c r="L1" s="21"/>
       <c r="M1" s="21"/>
       <c r="N1" s="21"/>
       <c r="O1" s="21"/>
       <c r="P1" s="21"/>
-    </row>
-    <row r="2" spans="1:16" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+    </row>
+    <row r="2" spans="1:18" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
@@ -1099,41 +1106,47 @@
         <v>31</v>
       </c>
       <c r="F2" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="J2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="L2" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>37</v>
-      </c>
       <c r="M2" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P2" s="22" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
+      <c r="Q2" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
@@ -1149,8 +1162,10 @@
       <c r="N3" s="23"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
-    </row>
-    <row r="4" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+    </row>
+    <row r="4" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1199,8 +1214,14 @@
       <c r="P4" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="5">
+        <v>17</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1213,16 +1234,18 @@
       <c r="F5" s="14"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="15"/>
-      <c r="K5" s="14"/>
+      <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
-    </row>
-    <row r="6" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1235,16 +1258,18 @@
       <c r="F6" s="14"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="15"/>
-      <c r="K6" s="14"/>
+      <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
-    </row>
-    <row r="7" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+    </row>
+    <row r="7" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -1255,16 +1280,18 @@
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="I7" s="16"/>
       <c r="J7" s="17"/>
-      <c r="K7" s="16"/>
+      <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
-    </row>
-    <row r="8" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+    </row>
+    <row r="8" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -1277,16 +1304,18 @@
       <c r="F8" s="14"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="15"/>
-      <c r="K8" s="14"/>
+      <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
-    </row>
-    <row r="9" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -1299,16 +1328,18 @@
       <c r="F9" s="14"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="15"/>
-      <c r="K9" s="14"/>
+      <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
-    </row>
-    <row r="10" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+    </row>
+    <row r="10" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -1321,16 +1352,18 @@
       <c r="F10" s="14"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="I10" s="14"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="14"/>
+      <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
-    </row>
-    <row r="11" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+    </row>
+    <row r="11" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6</v>
       </c>
@@ -1343,16 +1376,18 @@
       <c r="F11" s="14"/>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="14"/>
+      <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
-    </row>
-    <row r="12" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>7</v>
       </c>
@@ -1365,16 +1400,18 @@
       <c r="F12" s="14"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="14"/>
+      <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
-    </row>
-    <row r="13" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+    </row>
+    <row r="13" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -1387,16 +1424,18 @@
       <c r="F13" s="14"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="15"/>
-      <c r="K13" s="14"/>
+      <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
-    </row>
-    <row r="14" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+    </row>
+    <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -1409,16 +1448,18 @@
       <c r="F14" s="14"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="15"/>
-      <c r="K14" s="14"/>
+      <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
-    </row>
-    <row r="15" spans="1:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+    </row>
+    <row r="15" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
@@ -1435,8 +1476,10 @@
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
       <c r="P15" s="18"/>
-    </row>
-    <row r="16" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+    </row>
+    <row r="16" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>10</v>
       </c>
@@ -1449,16 +1492,18 @@
       <c r="F16" s="14"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="15"/>
-      <c r="K16" s="14"/>
+      <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
-    </row>
-    <row r="17" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+    </row>
+    <row r="17" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>11</v>
       </c>
@@ -1471,16 +1516,18 @@
       <c r="F17" s="14"/>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="15"/>
-      <c r="K17" s="14"/>
+      <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
-    </row>
-    <row r="18" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+    </row>
+    <row r="18" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>12</v>
       </c>
@@ -1493,36 +1540,40 @@
       <c r="F18" s="14"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="I18" s="14"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="14"/>
+      <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
-    </row>
-    <row r="19" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+    </row>
+    <row r="19" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="25"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="I19" s="19"/>
       <c r="J19" s="20"/>
-      <c r="K19" s="19"/>
+      <c r="K19" s="20"/>
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
       <c r="P19" s="20"/>
-    </row>
-    <row r="20" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>13</v>
       </c>
@@ -1535,16 +1586,18 @@
       <c r="F20" s="14"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="15"/>
-      <c r="K20" s="14"/>
+      <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
-    </row>
-    <row r="21" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+    </row>
+    <row r="21" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -1557,16 +1610,18 @@
       <c r="F21" s="14"/>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="15"/>
-      <c r="K21" s="14"/>
+      <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
-    </row>
-    <row r="22" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+    </row>
+    <row r="22" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>15</v>
       </c>
@@ -1579,16 +1634,18 @@
       <c r="F22" s="14"/>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="15"/>
-      <c r="K22" s="14"/>
+      <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
-    </row>
-    <row r="23" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+    </row>
+    <row r="23" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>16</v>
       </c>
@@ -1601,16 +1658,18 @@
       <c r="F23" s="14"/>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="15"/>
-      <c r="K23" s="14"/>
+      <c r="K23" s="15"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
-    </row>
-    <row r="24" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+    </row>
+    <row r="24" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>17</v>
       </c>
@@ -1623,16 +1682,18 @@
       <c r="F24" s="14"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="15"/>
-      <c r="K24" s="14"/>
+      <c r="K24" s="15"/>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
-    </row>
-    <row r="25" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+    </row>
+    <row r="25" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>18</v>
       </c>
@@ -1645,16 +1706,18 @@
       <c r="F25" s="14"/>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="15"/>
-      <c r="K25" s="14"/>
+      <c r="K25" s="15"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
-    </row>
-    <row r="26" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+    </row>
+    <row r="26" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>19</v>
       </c>
@@ -1667,16 +1730,18 @@
       <c r="F26" s="14"/>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="I26" s="14"/>
       <c r="J26" s="15"/>
-      <c r="K26" s="14"/>
+      <c r="K26" s="15"/>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
-    </row>
-    <row r="27" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+    </row>
+    <row r="27" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>20</v>
       </c>
@@ -1689,16 +1754,18 @@
       <c r="F27" s="14"/>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="15"/>
-      <c r="K27" s="14"/>
+      <c r="K27" s="15"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
-    </row>
-    <row r="28" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+    </row>
+    <row r="28" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>21</v>
       </c>
@@ -1711,16 +1778,18 @@
       <c r="F28" s="14"/>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="15"/>
-      <c r="K28" s="14"/>
+      <c r="K28" s="15"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
-    </row>
-    <row r="29" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+    </row>
+    <row r="29" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>22</v>
       </c>
@@ -1733,77 +1802,85 @@
       <c r="F29" s="14"/>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="15"/>
-      <c r="K29" s="14"/>
+      <c r="K29" s="15"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
-    </row>
-    <row r="30" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+    </row>
+    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="25"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="I30" s="19"/>
       <c r="J30" s="20"/>
-      <c r="K30" s="19"/>
+      <c r="K30" s="20"/>
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
       <c r="O30" s="20"/>
       <c r="P30" s="20"/>
-    </row>
-    <row r="31" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+    </row>
+    <row r="31" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="24"/>
+      <c r="B31" s="26"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="19"/>
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="I31" s="19"/>
       <c r="J31" s="20"/>
-      <c r="K31" s="19"/>
+      <c r="K31" s="20"/>
       <c r="L31" s="20"/>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
       <c r="O31" s="20"/>
       <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="G2:G3"/>
+  <mergeCells count="22">
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="O2:O3"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="J2:J3"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
